--- a/result/TEMPORAL_TEMPORAL_ts-400_tssi-10_vth-1.0_tc-20_tw-80_tfs-80_tfd-80_trained_data-60000.xlsx
+++ b/result/TEMPORAL_TEMPORAL_ts-400_tssi-10_vth-1.0_tc-20_tw-80_tfs-80_tfd-80_trained_data-60000.xlsx
@@ -393,7 +393,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -410,7 +410,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -427,7 +427,7 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -444,7 +444,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -461,7 +461,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -478,7 +478,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -495,7 +495,7 @@
         <v>70</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -512,7 +512,7 @@
         <v>80</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -529,13 +529,13 @@
         <v>90</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C10" t="n">
-        <v>33.2652</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>33.2652</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -546,13 +546,13 @@
         <v>100</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C11" t="n">
-        <v>165.0617</v>
+        <v>0.2166</v>
       </c>
       <c r="D11" t="n">
-        <v>165.0617</v>
+        <v>0.2166</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>110</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C12" t="n">
-        <v>359.3542</v>
+        <v>15.515</v>
       </c>
       <c r="D12" t="n">
-        <v>359.3542</v>
+        <v>15.515</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -580,13 +580,13 @@
         <v>120</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C13" t="n">
-        <v>815.5544</v>
+        <v>293.7189</v>
       </c>
       <c r="D13" t="n">
-        <v>815.5544</v>
+        <v>293.7189</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -597,13 +597,13 @@
         <v>130</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C14" t="n">
-        <v>972.9041999999999</v>
+        <v>1687.2729</v>
       </c>
       <c r="D14" t="n">
-        <v>972.9041999999999</v>
+        <v>1687.2729</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -614,13 +614,13 @@
         <v>140</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C15" t="n">
-        <v>1089.964</v>
+        <v>5672.6724</v>
       </c>
       <c r="D15" t="n">
-        <v>1089.964</v>
+        <v>5672.6724</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -631,13 +631,13 @@
         <v>150</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C16" t="n">
-        <v>1171.6651</v>
+        <v>13138.0425</v>
       </c>
       <c r="D16" t="n">
-        <v>1171.6651</v>
+        <v>13138.0425</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -648,13 +648,13 @@
         <v>160</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1134999990463257</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C17" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="D17" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -665,16 +665,16 @@
         <v>170</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9833999872207642</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C18" t="n">
-        <v>1376.9966</v>
+        <v>21874.283</v>
       </c>
       <c r="D18" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E18" t="n">
-        <v>150.9422</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="19">
@@ -682,16 +682,16 @@
         <v>180</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9896000027656555</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C19" t="n">
-        <v>1574.9396</v>
+        <v>21875.3584</v>
       </c>
       <c r="D19" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E19" t="n">
-        <v>348.8852</v>
+        <v>1.0933</v>
       </c>
     </row>
     <row r="20">
@@ -699,16 +699,16 @@
         <v>190</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9911999702453613</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C20" t="n">
-        <v>1789.6946</v>
+        <v>21900.4376</v>
       </c>
       <c r="D20" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E20" t="n">
-        <v>563.6402</v>
+        <v>26.1725</v>
       </c>
     </row>
     <row r="21">
@@ -716,16 +716,16 @@
         <v>200</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9918000102043152</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C21" t="n">
-        <v>1974.7613</v>
+        <v>22181.7454</v>
       </c>
       <c r="D21" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E21" t="n">
-        <v>748.7069</v>
+        <v>307.4803</v>
       </c>
     </row>
     <row r="22">
@@ -733,16 +733,16 @@
         <v>210</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9919999837875366</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C22" t="n">
-        <v>2113.7112</v>
+        <v>23809.3332</v>
       </c>
       <c r="D22" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E22" t="n">
-        <v>887.6568</v>
+        <v>1935.0681</v>
       </c>
     </row>
     <row r="23">
@@ -750,16 +750,16 @@
         <v>220</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9922999739646912</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C23" t="n">
-        <v>2210.4016</v>
+        <v>28180.1297</v>
       </c>
       <c r="D23" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E23" t="n">
-        <v>984.3472</v>
+        <v>6305.8646</v>
       </c>
     </row>
     <row r="24">
@@ -767,16 +767,16 @@
         <v>230</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9922999739646912</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C24" t="n">
-        <v>2274.5949</v>
+        <v>33897.5353</v>
       </c>
       <c r="D24" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E24" t="n">
-        <v>1048.5405</v>
+        <v>12023.2702</v>
       </c>
     </row>
     <row r="25">
@@ -784,16 +784,16 @@
         <v>240</v>
       </c>
       <c r="B25" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C25" t="n">
-        <v>2316.3305</v>
+        <v>38689.0123</v>
       </c>
       <c r="D25" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E25" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="26">
@@ -801,16 +801,16 @@
         <v>250</v>
       </c>
       <c r="B26" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C26" t="n">
-        <v>2316.3305</v>
+        <v>38689.1889</v>
       </c>
       <c r="D26" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E26" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="27">
@@ -818,16 +818,16 @@
         <v>260</v>
       </c>
       <c r="B27" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C27" t="n">
-        <v>2316.3305</v>
+        <v>38701.5218</v>
       </c>
       <c r="D27" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E27" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="28">
@@ -835,16 +835,16 @@
         <v>270</v>
       </c>
       <c r="B28" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C28" t="n">
-        <v>2316.3305</v>
+        <v>38968.1365</v>
       </c>
       <c r="D28" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E28" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="29">
@@ -852,16 +852,16 @@
         <v>280</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C29" t="n">
-        <v>2316.3305</v>
+        <v>40417.4271</v>
       </c>
       <c r="D29" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E29" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="30">
@@ -869,16 +869,16 @@
         <v>290</v>
       </c>
       <c r="B30" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C30" t="n">
-        <v>2316.3305</v>
+        <v>43217.4542</v>
       </c>
       <c r="D30" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E30" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="31">
@@ -886,16 +886,16 @@
         <v>300</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C31" t="n">
-        <v>2316.3305</v>
+        <v>45971.187</v>
       </c>
       <c r="D31" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E31" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="32">
@@ -903,16 +903,16 @@
         <v>310</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C32" t="n">
-        <v>2316.3305</v>
+        <v>47913.3082</v>
       </c>
       <c r="D32" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E32" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="33">
@@ -920,16 +920,16 @@
         <v>320</v>
       </c>
       <c r="B33" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C33" t="n">
-        <v>2316.3305</v>
+        <v>49127.711</v>
       </c>
       <c r="D33" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E33" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="34">
@@ -937,16 +937,16 @@
         <v>330</v>
       </c>
       <c r="B34" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C34" t="n">
-        <v>2316.3305</v>
+        <v>49129.1725</v>
       </c>
       <c r="D34" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E34" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="35">
@@ -954,16 +954,16 @@
         <v>340</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C35" t="n">
-        <v>2316.3305</v>
+        <v>49179.3993</v>
       </c>
       <c r="D35" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E35" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="36">
@@ -971,16 +971,16 @@
         <v>350</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C36" t="n">
-        <v>2316.3305</v>
+        <v>49499.6308</v>
       </c>
       <c r="D36" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E36" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="37">
@@ -988,16 +988,16 @@
         <v>360</v>
       </c>
       <c r="B37" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C37" t="n">
-        <v>2316.3305</v>
+        <v>50232.6506</v>
       </c>
       <c r="D37" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E37" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="38">
@@ -1005,16 +1005,16 @@
         <v>370</v>
       </c>
       <c r="B38" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C38" t="n">
-        <v>2316.3305</v>
+        <v>51177.3652</v>
       </c>
       <c r="D38" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E38" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="39">
@@ -1022,16 +1022,16 @@
         <v>380</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C39" t="n">
-        <v>2316.3305</v>
+        <v>52025.8986</v>
       </c>
       <c r="D39" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E39" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="40">
@@ -1039,16 +1039,16 @@
         <v>390</v>
       </c>
       <c r="B40" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C40" t="n">
-        <v>2316.3305</v>
+        <v>52646.9465</v>
       </c>
       <c r="D40" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E40" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
     <row r="41">
@@ -1056,16 +1056,16 @@
         <v>400</v>
       </c>
       <c r="B41" t="n">
-        <v>0.9922000169754028</v>
+        <v>0.1000000014901161</v>
       </c>
       <c r="C41" t="n">
-        <v>2316.3305</v>
+        <v>53053.9766</v>
       </c>
       <c r="D41" t="n">
-        <v>1226.0544</v>
+        <v>21874.2651</v>
       </c>
       <c r="E41" t="n">
-        <v>1090.2761</v>
+        <v>16814.7472</v>
       </c>
     </row>
   </sheetData>
